--- a/snapshots/2026-08-21.xlsx
+++ b/snapshots/2026-08-21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\agristack\UPLOAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50DDAAD-1A1B-4ACC-95AA-AF305CAD0EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD62B39A-A878-4ABA-B578-9E25A700644F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$E$1:$E$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$B$1:$B$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -1263,22 +1263,22 @@
         <v>105</v>
       </c>
       <c r="J2" s="20">
-        <v>1767</v>
+        <v>286</v>
       </c>
       <c r="K2" s="20">
-        <v>1683</v>
+        <v>0</v>
       </c>
       <c r="L2" s="20">
         <v>0</v>
       </c>
       <c r="M2" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" s="20">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O2" s="20">
-        <v>47</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1311,10 +1311,10 @@
         <v>10</v>
       </c>
       <c r="J3" s="20">
-        <v>1637</v>
+        <v>459</v>
       </c>
       <c r="K3" s="20">
-        <v>1593</v>
+        <v>98</v>
       </c>
       <c r="L3" s="20">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="N3" s="20">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O3" s="20">
-        <v>20</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1359,7 +1359,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="20">
-        <v>387</v>
+        <v>36</v>
       </c>
       <c r="K4" s="20">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="20">
-        <v>387</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1407,22 +1407,22 @@
         <v>1</v>
       </c>
       <c r="J5" s="20">
-        <v>1981</v>
+        <v>1767</v>
       </c>
       <c r="K5" s="20">
-        <v>1</v>
+        <v>1683</v>
       </c>
       <c r="L5" s="20">
         <v>0</v>
       </c>
       <c r="M5" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" s="20">
-        <v>1835</v>
+        <v>35</v>
       </c>
       <c r="O5" s="20">
-        <v>145</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1455,10 +1455,10 @@
         <v>4</v>
       </c>
       <c r="J6" s="20">
-        <v>1957</v>
+        <v>1981</v>
       </c>
       <c r="K6" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="20">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="20">
-        <v>0</v>
+        <v>1835</v>
       </c>
       <c r="O6" s="20">
-        <v>1957</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1503,22 +1503,22 @@
         <v>12</v>
       </c>
       <c r="J7" s="20">
-        <v>1338</v>
+        <v>643</v>
       </c>
       <c r="K7" s="20">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="L7" s="20">
         <v>0</v>
       </c>
       <c r="M7" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="20">
-        <v>991</v>
+        <v>208</v>
       </c>
       <c r="O7" s="20">
-        <v>347</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -1551,22 +1551,22 @@
         <v>13</v>
       </c>
       <c r="J8" s="20">
-        <v>908</v>
+        <v>1070</v>
       </c>
       <c r="K8" s="20">
-        <v>814</v>
+        <v>227</v>
       </c>
       <c r="L8" s="20">
         <v>0</v>
       </c>
       <c r="M8" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" s="20">
-        <v>90</v>
+        <v>376</v>
       </c>
       <c r="O8" s="20">
-        <v>4</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
@@ -1599,10 +1599,10 @@
         <v>84</v>
       </c>
       <c r="J9" s="20">
-        <v>1549</v>
+        <v>1451</v>
       </c>
       <c r="K9" s="20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L9" s="20">
         <v>1</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="20">
-        <v>1459</v>
+        <v>731</v>
       </c>
       <c r="O9" s="20">
-        <v>52</v>
+        <v>719</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1647,22 +1647,22 @@
         <v>5</v>
       </c>
       <c r="J10" s="20">
-        <v>1520</v>
+        <v>1957</v>
       </c>
       <c r="K10" s="20">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L10" s="20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M10" s="20">
         <v>0</v>
       </c>
       <c r="N10" s="20">
-        <v>1460</v>
+        <v>0</v>
       </c>
       <c r="O10" s="20">
-        <v>25</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -1695,22 +1695,22 @@
         <v>14</v>
       </c>
       <c r="J11" s="20">
-        <v>459</v>
+        <v>816</v>
       </c>
       <c r="K11" s="20">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="L11" s="20">
         <v>0</v>
       </c>
       <c r="M11" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="20">
         <v>0</v>
       </c>
       <c r="O11" s="20">
-        <v>361</v>
+        <v>812</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -1743,7 +1743,7 @@
         <v>15</v>
       </c>
       <c r="J12" s="20">
-        <v>36</v>
+        <v>215</v>
       </c>
       <c r="K12" s="20">
         <v>0</v>
@@ -1755,10 +1755,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="20">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="O12" s="20">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -1791,22 +1791,22 @@
         <v>106</v>
       </c>
       <c r="J13" s="20">
-        <v>643</v>
+        <v>500</v>
       </c>
       <c r="K13" s="20">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="L13" s="20">
         <v>0</v>
       </c>
       <c r="M13" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="20">
-        <v>208</v>
+        <v>474</v>
       </c>
       <c r="O13" s="20">
-        <v>119</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1839,22 +1839,22 @@
         <v>52</v>
       </c>
       <c r="J14" s="20">
-        <v>1070</v>
+        <v>732</v>
       </c>
       <c r="K14" s="20">
-        <v>227</v>
+        <v>482</v>
       </c>
       <c r="L14" s="20">
         <v>0</v>
       </c>
       <c r="M14" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N14" s="20">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="O14" s="20">
-        <v>465</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1887,22 +1887,22 @@
         <v>62</v>
       </c>
       <c r="J15" s="20">
-        <v>816</v>
+        <v>637</v>
       </c>
       <c r="K15" s="20">
-        <v>3</v>
+        <v>634</v>
       </c>
       <c r="L15" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="20">
+        <v>0</v>
+      </c>
+      <c r="N15" s="20">
         <v>1</v>
       </c>
-      <c r="N15" s="20">
-        <v>0</v>
-      </c>
       <c r="O15" s="20">
-        <v>812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="20">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K16" s="20">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="L16" s="20">
         <v>0</v>
@@ -1947,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="N16" s="20">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="O16" s="20">
-        <v>108</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -1983,10 +1983,10 @@
         <v>107</v>
       </c>
       <c r="J17" s="20">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="K17" s="20">
-        <v>148</v>
+        <v>2</v>
       </c>
       <c r="L17" s="20">
         <v>0</v>
@@ -1995,10 +1995,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="20">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="O17" s="20">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2175,10 +2175,10 @@
         <v>108</v>
       </c>
       <c r="J21" s="20">
-        <v>257</v>
+        <v>129</v>
       </c>
       <c r="K21" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="20">
         <v>0</v>
@@ -2187,10 +2187,10 @@
         <v>0</v>
       </c>
       <c r="N21" s="20">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="O21" s="20">
-        <v>257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2223,10 +2223,10 @@
         <v>109</v>
       </c>
       <c r="J22" s="20">
-        <v>554</v>
+        <v>260</v>
       </c>
       <c r="K22" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="20">
         <v>0</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="N22" s="20">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="O22" s="20">
-        <v>554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2271,7 +2271,7 @@
         <v>19</v>
       </c>
       <c r="J23" s="20">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="K23" s="20">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="20">
-        <v>319</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2319,22 +2319,22 @@
         <v>63</v>
       </c>
       <c r="J24" s="20">
-        <v>1043</v>
+        <v>771</v>
       </c>
       <c r="K24" s="20">
-        <v>683</v>
+        <v>764</v>
       </c>
       <c r="L24" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="20">
         <v>0</v>
       </c>
       <c r="N24" s="20">
-        <v>315</v>
+        <v>1</v>
       </c>
       <c r="O24" s="20">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2367,22 +2367,22 @@
         <v>21</v>
       </c>
       <c r="J25" s="20">
-        <v>1419</v>
+        <v>319</v>
       </c>
       <c r="K25" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="20">
         <v>0</v>
       </c>
       <c r="M25" s="20">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N25" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="20">
-        <v>1409</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2415,7 +2415,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="20">
-        <v>618</v>
+        <v>554</v>
       </c>
       <c r="K26" s="20">
         <v>0</v>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="20">
-        <v>618</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2463,22 +2463,22 @@
         <v>85</v>
       </c>
       <c r="J27" s="20">
-        <v>288</v>
+        <v>1531</v>
       </c>
       <c r="K27" s="20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L27" s="20">
+        <v>0</v>
+      </c>
+      <c r="M27" s="20">
         <v>1</v>
       </c>
-      <c r="M27" s="20">
-        <v>9</v>
-      </c>
       <c r="N27" s="20">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="O27" s="20">
-        <v>12</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2511,10 +2511,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="20">
-        <v>2248</v>
+        <v>1043</v>
       </c>
       <c r="K28" s="20">
-        <v>1297</v>
+        <v>683</v>
       </c>
       <c r="L28" s="20">
         <v>0</v>
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="N28" s="20">
-        <v>373</v>
+        <v>315</v>
       </c>
       <c r="O28" s="20">
-        <v>578</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2559,22 +2559,22 @@
         <v>23</v>
       </c>
       <c r="J29" s="20">
-        <v>303</v>
+        <v>1419</v>
       </c>
       <c r="K29" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="20">
         <v>0</v>
       </c>
       <c r="M29" s="20">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N29" s="20">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="O29" s="20">
-        <v>145</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2607,7 +2607,7 @@
         <v>24</v>
       </c>
       <c r="J30" s="20">
-        <v>2</v>
+        <v>618</v>
       </c>
       <c r="K30" s="20">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="20">
-        <v>2</v>
+        <v>618</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2655,10 +2655,10 @@
         <v>53</v>
       </c>
       <c r="J31" s="20">
-        <v>631</v>
+        <v>274</v>
       </c>
       <c r="K31" s="20">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="L31" s="20">
         <v>0</v>
@@ -2667,10 +2667,10 @@
         <v>0</v>
       </c>
       <c r="N31" s="20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O31" s="20">
-        <v>621</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2703,10 +2703,10 @@
         <v>110</v>
       </c>
       <c r="J32" s="20">
-        <v>972</v>
+        <v>95</v>
       </c>
       <c r="K32" s="20">
-        <v>881</v>
+        <v>0</v>
       </c>
       <c r="L32" s="20">
         <v>0</v>
@@ -2715,10 +2715,10 @@
         <v>0</v>
       </c>
       <c r="N32" s="20">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="O32" s="20">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2751,7 +2751,7 @@
         <v>86</v>
       </c>
       <c r="J33" s="20">
-        <v>497</v>
+        <v>371</v>
       </c>
       <c r="K33" s="20">
         <v>0</v>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="O33" s="20">
-        <v>497</v>
+        <v>371</v>
       </c>
     </row>
     <row r="34" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2799,22 +2799,22 @@
         <v>25</v>
       </c>
       <c r="J34" s="20">
-        <v>416</v>
+        <v>288</v>
       </c>
       <c r="K34" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N34" s="20">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="O34" s="20">
-        <v>233</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2847,22 +2847,22 @@
         <v>87</v>
       </c>
       <c r="J35" s="20">
-        <v>5</v>
+        <v>1028</v>
       </c>
       <c r="K35" s="20">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="L35" s="20">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M35" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" s="20">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="O35" s="20">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -2895,10 +2895,10 @@
         <v>26</v>
       </c>
       <c r="J36" s="20">
-        <v>304</v>
+        <v>2248</v>
       </c>
       <c r="K36" s="20">
-        <v>55</v>
+        <v>1297</v>
       </c>
       <c r="L36" s="20">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="N36" s="20">
-        <v>189</v>
+        <v>373</v>
       </c>
       <c r="O36" s="20">
-        <v>60</v>
+        <v>578</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2943,22 +2943,22 @@
         <v>88</v>
       </c>
       <c r="J37" s="20">
-        <v>142</v>
+        <v>1048</v>
       </c>
       <c r="K37" s="20">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L37" s="20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M37" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="20">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O37" s="20">
-        <v>142</v>
+        <v>639</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -2991,10 +2991,10 @@
         <v>111</v>
       </c>
       <c r="J38" s="20">
-        <v>779</v>
+        <v>196</v>
       </c>
       <c r="K38" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="20">
         <v>0</v>
@@ -3003,10 +3003,10 @@
         <v>0</v>
       </c>
       <c r="N38" s="20">
-        <v>439</v>
+        <v>193</v>
       </c>
       <c r="O38" s="20">
-        <v>338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3039,22 +3039,22 @@
         <v>64</v>
       </c>
       <c r="J39" s="20">
-        <v>410</v>
+        <v>19</v>
       </c>
       <c r="K39" s="20">
         <v>0</v>
       </c>
       <c r="L39" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="20">
         <v>0</v>
       </c>
       <c r="N39" s="20">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="O39" s="20">
-        <v>116</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3087,10 +3087,10 @@
         <v>54</v>
       </c>
       <c r="J40" s="20">
-        <v>1</v>
+        <v>661</v>
       </c>
       <c r="K40" s="20">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="L40" s="20">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3135,22 +3135,22 @@
         <v>54</v>
       </c>
       <c r="J41" s="20">
-        <v>582</v>
+        <v>842</v>
       </c>
       <c r="K41" s="20">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="L41" s="20">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M41" s="20">
         <v>0</v>
       </c>
       <c r="N41" s="20">
-        <v>423</v>
+        <v>161</v>
       </c>
       <c r="O41" s="20">
-        <v>159</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3183,7 +3183,7 @@
         <v>27</v>
       </c>
       <c r="J42" s="20">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="K42" s="20">
         <v>0</v>
@@ -3195,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="N42" s="20">
-        <v>309</v>
+        <v>158</v>
       </c>
       <c r="O42" s="20">
-        <v>11</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3231,10 +3231,10 @@
         <v>112</v>
       </c>
       <c r="J43" s="20">
-        <v>535</v>
+        <v>224</v>
       </c>
       <c r="K43" s="20">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L43" s="20">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="20">
-        <v>508</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3279,7 +3279,7 @@
         <v>29</v>
       </c>
       <c r="J44" s="20">
-        <v>1560</v>
+        <v>631</v>
       </c>
       <c r="K44" s="20">
         <v>0</v>
@@ -3291,10 +3291,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="20">
-        <v>1360</v>
+        <v>10</v>
       </c>
       <c r="O44" s="20">
-        <v>200</v>
+        <v>621</v>
       </c>
     </row>
     <row r="45" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3327,22 +3327,22 @@
         <v>66</v>
       </c>
       <c r="J45" s="20">
-        <v>881</v>
+        <v>315</v>
       </c>
       <c r="K45" s="20">
         <v>0</v>
       </c>
       <c r="L45" s="20">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M45" s="20">
         <v>0</v>
       </c>
       <c r="N45" s="20">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="O45" s="20">
-        <v>880</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3375,22 +3375,22 @@
         <v>67</v>
       </c>
       <c r="J46" s="20">
-        <v>660</v>
+        <v>275</v>
       </c>
       <c r="K46" s="20">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L46" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" s="20">
         <v>0</v>
       </c>
       <c r="N46" s="20">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="O46" s="20">
-        <v>660</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3423,7 +3423,7 @@
         <v>69</v>
       </c>
       <c r="J47" s="20">
-        <v>1001</v>
+        <v>6</v>
       </c>
       <c r="K47" s="20">
         <v>0</v>
@@ -3432,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="M47" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="20">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="O47" s="20">
-        <v>802</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3471,22 +3471,22 @@
         <v>70</v>
       </c>
       <c r="J48" s="20">
-        <v>208</v>
+        <v>1525</v>
       </c>
       <c r="K48" s="20">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L48" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N48" s="20">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="O48" s="20">
-        <v>208</v>
+        <v>808</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3519,7 +3519,7 @@
         <v>65</v>
       </c>
       <c r="J49" s="20">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="K49" s="20">
         <v>0</v>
@@ -3531,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="20">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="O49" s="20">
-        <v>13</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3567,10 +3567,10 @@
         <v>89</v>
       </c>
       <c r="J50" s="20">
-        <v>159</v>
+        <v>532</v>
       </c>
       <c r="K50" s="20">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="L50" s="20">
         <v>0</v>
@@ -3582,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="20">
-        <v>13</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3615,22 +3615,22 @@
         <v>28</v>
       </c>
       <c r="J51" s="20">
-        <v>582</v>
+        <v>2</v>
       </c>
       <c r="K51" s="20">
         <v>0</v>
       </c>
       <c r="L51" s="20">
+        <v>0</v>
+      </c>
+      <c r="M51" s="20">
+        <v>0</v>
+      </c>
+      <c r="N51" s="20">
+        <v>0</v>
+      </c>
+      <c r="O51" s="20">
         <v>2</v>
-      </c>
-      <c r="M51" s="20">
-        <v>5</v>
-      </c>
-      <c r="N51" s="20">
-        <v>0</v>
-      </c>
-      <c r="O51" s="20">
-        <v>575</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3663,10 +3663,10 @@
         <v>68</v>
       </c>
       <c r="J52" s="20">
-        <v>976</v>
+        <v>332</v>
       </c>
       <c r="K52" s="20">
-        <v>4</v>
+        <v>324</v>
       </c>
       <c r="L52" s="20">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="N52" s="20">
-        <v>947</v>
+        <v>8</v>
       </c>
       <c r="O52" s="20">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3711,22 +3711,22 @@
         <v>61</v>
       </c>
       <c r="J53" s="20">
-        <v>1026</v>
+        <v>1914</v>
       </c>
       <c r="K53" s="20">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L53" s="20">
         <v>1</v>
       </c>
       <c r="M53" s="20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" s="20">
-        <v>0</v>
+        <v>1316</v>
       </c>
       <c r="O53" s="20">
-        <v>1025</v>
+        <v>580</v>
       </c>
     </row>
     <row r="54" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3759,22 +3759,22 @@
         <v>90</v>
       </c>
       <c r="J54" s="20">
-        <v>732</v>
+        <v>967</v>
       </c>
       <c r="K54" s="20">
-        <v>482</v>
+        <v>965</v>
       </c>
       <c r="L54" s="20">
         <v>0</v>
       </c>
       <c r="M54" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N54" s="20">
         <v>0</v>
       </c>
       <c r="O54" s="20">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3807,10 +3807,10 @@
         <v>113</v>
       </c>
       <c r="J55" s="20">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="K55" s="20">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="L55" s="20">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="20">
-        <v>95</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -3855,10 +3855,10 @@
         <v>114</v>
       </c>
       <c r="J56" s="20">
-        <v>661</v>
+        <v>571</v>
       </c>
       <c r="K56" s="20">
-        <v>661</v>
+        <v>3</v>
       </c>
       <c r="L56" s="20">
         <v>0</v>
@@ -3867,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="N56" s="20">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="O56" s="20">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>30</v>
       </c>
       <c r="J57" s="20">
-        <v>641</v>
+        <v>972</v>
       </c>
       <c r="K57" s="20">
-        <v>641</v>
+        <v>881</v>
       </c>
       <c r="L57" s="20">
         <v>0</v>
@@ -3915,10 +3915,10 @@
         <v>0</v>
       </c>
       <c r="N57" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="20">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3951,7 +3951,7 @@
         <v>71</v>
       </c>
       <c r="J58" s="20">
-        <v>718</v>
+        <v>319</v>
       </c>
       <c r="K58" s="20">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="M58" s="20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N58" s="20">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="O58" s="20">
-        <v>718</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -3999,10 +3999,10 @@
         <v>55</v>
       </c>
       <c r="J59" s="20">
-        <v>227</v>
+        <v>641</v>
       </c>
       <c r="K59" s="20">
-        <v>0</v>
+        <v>641</v>
       </c>
       <c r="L59" s="20">
         <v>0</v>
@@ -4014,7 +4014,7 @@
         <v>0</v>
       </c>
       <c r="O59" s="20">
-        <v>227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4047,10 +4047,10 @@
         <v>6</v>
       </c>
       <c r="J60" s="20">
-        <v>699</v>
+        <v>1338</v>
       </c>
       <c r="K60" s="20">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="L60" s="20">
         <v>0</v>
@@ -4059,10 +4059,10 @@
         <v>0</v>
       </c>
       <c r="N60" s="20">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="O60" s="20">
-        <v>65</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4095,7 +4095,7 @@
         <v>56</v>
       </c>
       <c r="J61" s="20">
-        <v>565</v>
+        <v>718</v>
       </c>
       <c r="K61" s="20">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="20">
-        <v>565</v>
+        <v>718</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4143,10 +4143,10 @@
         <v>31</v>
       </c>
       <c r="J62" s="20">
-        <v>1513</v>
+        <v>497</v>
       </c>
       <c r="K62" s="20">
-        <v>1496</v>
+        <v>0</v>
       </c>
       <c r="L62" s="20">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="20">
-        <v>17</v>
+        <v>497</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4191,22 +4191,22 @@
         <v>32</v>
       </c>
       <c r="J63" s="20">
-        <v>637</v>
+        <v>416</v>
       </c>
       <c r="K63" s="20">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="L63" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" s="20">
         <v>0</v>
       </c>
       <c r="N63" s="20">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="O63" s="20">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4239,22 +4239,22 @@
         <v>115</v>
       </c>
       <c r="J64" s="20">
-        <v>771</v>
+        <v>325</v>
       </c>
       <c r="K64" s="20">
-        <v>764</v>
+        <v>0</v>
       </c>
       <c r="L64" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="20">
         <v>0</v>
       </c>
       <c r="N64" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="20">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4287,7 +4287,7 @@
         <v>33</v>
       </c>
       <c r="J65" s="20">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K65" s="20">
         <v>0</v>
@@ -4302,7 +4302,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="20">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4335,22 +4335,22 @@
         <v>57</v>
       </c>
       <c r="J66" s="20">
-        <v>842</v>
+        <v>227</v>
       </c>
       <c r="K66" s="20">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="L66" s="20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M66" s="20">
         <v>0</v>
       </c>
       <c r="N66" s="20">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="O66" s="20">
-        <v>4</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4383,10 +4383,10 @@
         <v>72</v>
       </c>
       <c r="J67" s="20">
-        <v>265</v>
+        <v>894</v>
       </c>
       <c r="K67" s="20">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="L67" s="20">
         <v>0</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="20">
-        <v>265</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4431,22 +4431,22 @@
         <v>34</v>
       </c>
       <c r="J68" s="20">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="K68" s="20">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L68" s="20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M68" s="20">
         <v>0</v>
       </c>
       <c r="N68" s="20">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="O68" s="20">
-        <v>177</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4479,22 +4479,22 @@
         <v>35</v>
       </c>
       <c r="J69" s="20">
-        <v>275</v>
+        <v>142</v>
       </c>
       <c r="K69" s="20">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L69" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="20">
         <v>0</v>
       </c>
       <c r="N69" s="20">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="O69" s="20">
-        <v>23</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4527,10 +4527,10 @@
         <v>36</v>
       </c>
       <c r="J70" s="20">
-        <v>332</v>
+        <v>779</v>
       </c>
       <c r="K70" s="20">
-        <v>324</v>
+        <v>2</v>
       </c>
       <c r="L70" s="20">
         <v>0</v>
@@ -4539,10 +4539,10 @@
         <v>0</v>
       </c>
       <c r="N70" s="20">
-        <v>8</v>
+        <v>439</v>
       </c>
       <c r="O70" s="20">
-        <v>0</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4575,22 +4575,22 @@
         <v>37</v>
       </c>
       <c r="J71" s="20">
-        <v>6</v>
+        <v>410</v>
       </c>
       <c r="K71" s="20">
         <v>0</v>
       </c>
       <c r="L71" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="20">
         <v>0</v>
       </c>
       <c r="N71" s="20">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="O71" s="20">
-        <v>6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4623,22 +4623,22 @@
         <v>38</v>
       </c>
       <c r="J72" s="20">
-        <v>1525</v>
+        <v>1</v>
       </c>
       <c r="K72" s="20">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L72" s="20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" s="20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N72" s="20">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="O72" s="20">
-        <v>808</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4671,22 +4671,22 @@
         <v>73</v>
       </c>
       <c r="J73" s="20">
-        <v>1914</v>
+        <v>745</v>
       </c>
       <c r="K73" s="20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L73" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N73" s="20">
-        <v>1316</v>
+        <v>0</v>
       </c>
       <c r="O73" s="20">
-        <v>580</v>
+        <v>745</v>
       </c>
     </row>
     <row r="74" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4719,22 +4719,22 @@
         <v>7</v>
       </c>
       <c r="J74" s="20">
-        <v>319</v>
+        <v>908</v>
       </c>
       <c r="K74" s="20">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="L74" s="20">
         <v>0</v>
       </c>
       <c r="M74" s="20">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N74" s="20">
-        <v>278</v>
+        <v>90</v>
       </c>
       <c r="O74" s="20">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4767,10 +4767,10 @@
         <v>7</v>
       </c>
       <c r="J75" s="20">
-        <v>894</v>
+        <v>421</v>
       </c>
       <c r="K75" s="20">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="L75" s="20">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="O75" s="20">
-        <v>0</v>
+        <v>421</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4815,7 +4815,7 @@
         <v>91</v>
       </c>
       <c r="J76" s="20">
-        <v>745</v>
+        <v>206</v>
       </c>
       <c r="K76" s="20">
         <v>0</v>
@@ -4830,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="O76" s="20">
-        <v>745</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -4863,22 +4863,22 @@
         <v>8</v>
       </c>
       <c r="J77" s="20">
-        <v>1751</v>
+        <v>1549</v>
       </c>
       <c r="K77" s="20">
-        <v>634</v>
+        <v>37</v>
       </c>
       <c r="L77" s="20">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="M77" s="20">
         <v>0</v>
       </c>
       <c r="N77" s="20">
-        <v>449</v>
+        <v>1459</v>
       </c>
       <c r="O77" s="20">
-        <v>589</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4911,22 +4911,22 @@
         <v>39</v>
       </c>
       <c r="J78" s="20">
-        <v>683</v>
+        <v>582</v>
       </c>
       <c r="K78" s="20">
         <v>0</v>
       </c>
       <c r="L78" s="20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M78" s="20">
         <v>0</v>
       </c>
       <c r="N78" s="20">
-        <v>45</v>
+        <v>423</v>
       </c>
       <c r="O78" s="20">
-        <v>633</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -4959,10 +4959,10 @@
         <v>116</v>
       </c>
       <c r="J79" s="20">
-        <v>434</v>
+        <v>281</v>
       </c>
       <c r="K79" s="20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L79" s="20">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="N79" s="20">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="O79" s="20">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="80" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5007,10 +5007,10 @@
         <v>58</v>
       </c>
       <c r="J80" s="20">
-        <v>32</v>
+        <v>699</v>
       </c>
       <c r="K80" s="20">
-        <v>0</v>
+        <v>634</v>
       </c>
       <c r="L80" s="20">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>0</v>
       </c>
       <c r="O80" s="20">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5055,22 +5055,22 @@
         <v>59</v>
       </c>
       <c r="J81" s="20">
-        <v>1257</v>
+        <v>565</v>
       </c>
       <c r="K81" s="20">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L81" s="20">
         <v>0</v>
       </c>
       <c r="M81" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N81" s="20">
-        <v>793</v>
+        <v>0</v>
       </c>
       <c r="O81" s="20">
-        <v>411</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5103,22 +5103,22 @@
         <v>40</v>
       </c>
       <c r="J82" s="20">
-        <v>767</v>
+        <v>320</v>
       </c>
       <c r="K82" s="20">
         <v>0</v>
       </c>
       <c r="L82" s="20">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M82" s="20">
         <v>0</v>
       </c>
       <c r="N82" s="20">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="O82" s="20">
-        <v>362</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5151,22 +5151,22 @@
         <v>74</v>
       </c>
       <c r="J83" s="20">
-        <v>1064</v>
+        <v>1751</v>
       </c>
       <c r="K83" s="20">
-        <v>9</v>
+        <v>634</v>
       </c>
       <c r="L83" s="20">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M83" s="20">
         <v>0</v>
       </c>
       <c r="N83" s="20">
-        <v>1055</v>
+        <v>449</v>
       </c>
       <c r="O83" s="20">
-        <v>0</v>
+        <v>589</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5199,7 +5199,7 @@
         <v>92</v>
       </c>
       <c r="J84" s="20">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="K84" s="20">
         <v>0</v>
@@ -5214,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="O84" s="20">
-        <v>140</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5247,22 +5247,22 @@
         <v>41</v>
       </c>
       <c r="J85" s="20">
-        <v>676</v>
+        <v>535</v>
       </c>
       <c r="K85" s="20">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="L85" s="20">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M85" s="20">
         <v>0</v>
       </c>
       <c r="N85" s="20">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="O85" s="20">
-        <v>414</v>
+        <v>508</v>
       </c>
     </row>
     <row r="86" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5295,7 +5295,7 @@
         <v>117</v>
       </c>
       <c r="J86" s="20">
-        <v>626</v>
+        <v>53</v>
       </c>
       <c r="K86" s="20">
         <v>0</v>
@@ -5307,10 +5307,10 @@
         <v>0</v>
       </c>
       <c r="N86" s="20">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="O86" s="20">
-        <v>626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
@@ -5343,22 +5343,22 @@
         <v>2</v>
       </c>
       <c r="J87" s="20">
-        <v>1451</v>
+        <v>1637</v>
       </c>
       <c r="K87" s="20">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="L87" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="20">
         <v>0</v>
       </c>
       <c r="N87" s="20">
-        <v>731</v>
+        <v>24</v>
       </c>
       <c r="O87" s="20">
-        <v>719</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5391,22 +5391,22 @@
         <v>93</v>
       </c>
       <c r="J88" s="20">
-        <v>1531</v>
+        <v>558</v>
       </c>
       <c r="K88" s="20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L88" s="20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M88" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="20">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="O88" s="20">
-        <v>1530</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5439,22 +5439,22 @@
         <v>94</v>
       </c>
       <c r="J89" s="20">
-        <v>371</v>
+        <v>525</v>
       </c>
       <c r="K89" s="20">
         <v>0</v>
       </c>
       <c r="L89" s="20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M89" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N89" s="20">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="O89" s="20">
-        <v>371</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5487,22 +5487,22 @@
         <v>42</v>
       </c>
       <c r="J90" s="20">
-        <v>1028</v>
+        <v>1560</v>
       </c>
       <c r="K90" s="20">
-        <v>639</v>
+        <v>0</v>
       </c>
       <c r="L90" s="20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M90" s="20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N90" s="20">
-        <v>334</v>
+        <v>1360</v>
       </c>
       <c r="O90" s="20">
-        <v>41</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5535,22 +5535,22 @@
         <v>43</v>
       </c>
       <c r="J91" s="20">
-        <v>1048</v>
+        <v>881</v>
       </c>
       <c r="K91" s="20">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="L91" s="20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M91" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" s="20">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O91" s="20">
-        <v>639</v>
+        <v>880</v>
       </c>
     </row>
     <row r="92" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5583,7 +5583,7 @@
         <v>44</v>
       </c>
       <c r="J92" s="20">
-        <v>532</v>
+        <v>660</v>
       </c>
       <c r="K92" s="20">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="20">
-        <v>532</v>
+        <v>660</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5631,22 +5631,22 @@
         <v>75</v>
       </c>
       <c r="J93" s="20">
-        <v>967</v>
+        <v>683</v>
       </c>
       <c r="K93" s="20">
-        <v>965</v>
+        <v>0</v>
       </c>
       <c r="L93" s="20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M93" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N93" s="20">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O93" s="20">
-        <v>0</v>
+        <v>633</v>
       </c>
     </row>
     <row r="94" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -5679,7 +5679,7 @@
         <v>118</v>
       </c>
       <c r="J94" s="20">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="K94" s="20">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="O94" s="20">
-        <v>206</v>
+        <v>166</v>
       </c>
     </row>
     <row r="95" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5727,7 +5727,7 @@
         <v>45</v>
       </c>
       <c r="J95" s="20">
-        <v>230</v>
+        <v>1001</v>
       </c>
       <c r="K95" s="20">
         <v>0</v>
@@ -5736,13 +5736,13 @@
         <v>0</v>
       </c>
       <c r="M95" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" s="20">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="O95" s="20">
-        <v>230</v>
+        <v>802</v>
       </c>
     </row>
     <row r="96" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5775,22 +5775,22 @@
         <v>9</v>
       </c>
       <c r="J96" s="20">
-        <v>558</v>
+        <v>1520</v>
       </c>
       <c r="K96" s="20">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L96" s="20">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="M96" s="20">
         <v>0</v>
       </c>
       <c r="N96" s="20">
-        <v>304</v>
+        <v>1460</v>
       </c>
       <c r="O96" s="20">
-        <v>202</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5823,22 +5823,22 @@
         <v>76</v>
       </c>
       <c r="J97" s="20">
-        <v>525</v>
+        <v>434</v>
       </c>
       <c r="K97" s="20">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L97" s="20">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M97" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N97" s="20">
-        <v>487</v>
+        <v>397</v>
       </c>
       <c r="O97" s="20">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
@@ -5919,22 +5919,22 @@
         <v>77</v>
       </c>
       <c r="J99" s="20">
-        <v>902</v>
+        <v>32</v>
       </c>
       <c r="K99" s="20">
-        <v>752</v>
+        <v>0</v>
       </c>
       <c r="L99" s="20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M99" s="20">
         <v>0</v>
       </c>
       <c r="N99" s="20">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="O99" s="20">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -5967,22 +5967,22 @@
         <v>96</v>
       </c>
       <c r="J100" s="20">
-        <v>2218</v>
+        <v>902</v>
       </c>
       <c r="K100" s="20">
-        <v>114</v>
+        <v>752</v>
       </c>
       <c r="L100" s="20">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M100" s="20">
         <v>0</v>
       </c>
       <c r="N100" s="20">
-        <v>1985</v>
+        <v>122</v>
       </c>
       <c r="O100" s="20">
-        <v>118</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
@@ -6015,22 +6015,22 @@
         <v>97</v>
       </c>
       <c r="J101" s="20">
-        <v>2205</v>
+        <v>2218</v>
       </c>
       <c r="K101" s="20">
-        <v>1101</v>
+        <v>114</v>
       </c>
       <c r="L101" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" s="20">
-        <v>1039</v>
+        <v>1985</v>
       </c>
       <c r="O101" s="20">
-        <v>64</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -6063,7 +6063,7 @@
         <v>3</v>
       </c>
       <c r="J102" s="20">
-        <v>678</v>
+        <v>387</v>
       </c>
       <c r="K102" s="20">
         <v>0</v>
@@ -6078,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="O102" s="20">
-        <v>678</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -6111,22 +6111,22 @@
         <v>78</v>
       </c>
       <c r="J103" s="20">
-        <v>687</v>
+        <v>1257</v>
       </c>
       <c r="K103" s="20">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="L103" s="20">
         <v>0</v>
       </c>
       <c r="M103" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N103" s="20">
-        <v>0</v>
+        <v>793</v>
       </c>
       <c r="O103" s="20">
-        <v>685</v>
+        <v>411</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6159,22 +6159,22 @@
         <v>119</v>
       </c>
       <c r="J104" s="20">
-        <v>567</v>
+        <v>496</v>
       </c>
       <c r="K104" s="20">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="L104" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M104" s="20">
         <v>0</v>
       </c>
       <c r="N104" s="20">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="O104" s="20">
-        <v>82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6207,22 +6207,22 @@
         <v>98</v>
       </c>
       <c r="J105" s="20">
-        <v>1134</v>
+        <v>2205</v>
       </c>
       <c r="K105" s="20">
-        <v>37</v>
+        <v>1101</v>
       </c>
       <c r="L105" s="20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M105" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" s="20">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="O105" s="20">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6255,22 +6255,22 @@
         <v>79</v>
       </c>
       <c r="J106" s="20">
-        <v>923</v>
+        <v>767</v>
       </c>
       <c r="K106" s="20">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="L106" s="20">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M106" s="20">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="N106" s="20">
-        <v>13</v>
+        <v>355</v>
       </c>
       <c r="O106" s="20">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6303,7 +6303,7 @@
         <v>99</v>
       </c>
       <c r="J107" s="20">
-        <v>402</v>
+        <v>678</v>
       </c>
       <c r="K107" s="20">
         <v>0</v>
@@ -6318,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="O107" s="20">
-        <v>402</v>
+        <v>678</v>
       </c>
     </row>
     <row r="108" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6351,10 +6351,10 @@
         <v>80</v>
       </c>
       <c r="J108" s="20">
-        <v>286</v>
+        <v>1064</v>
       </c>
       <c r="K108" s="20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L108" s="20">
         <v>0</v>
@@ -6363,10 +6363,10 @@
         <v>0</v>
       </c>
       <c r="N108" s="20">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="O108" s="20">
-        <v>286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -6399,10 +6399,10 @@
         <v>60</v>
       </c>
       <c r="J109" s="20">
-        <v>500</v>
+        <v>1513</v>
       </c>
       <c r="K109" s="20">
-        <v>0</v>
+        <v>1496</v>
       </c>
       <c r="L109" s="20">
         <v>0</v>
@@ -6411,10 +6411,10 @@
         <v>0</v>
       </c>
       <c r="N109" s="20">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="O109" s="20">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6447,10 +6447,10 @@
         <v>46</v>
       </c>
       <c r="J110" s="20">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="K110" s="20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="20">
         <v>0</v>
@@ -6459,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="N110" s="20">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="O110" s="20">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
@@ -6495,22 +6495,22 @@
         <v>100</v>
       </c>
       <c r="J111" s="20">
-        <v>129</v>
+        <v>687</v>
       </c>
       <c r="K111" s="20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L111" s="20">
         <v>0</v>
       </c>
       <c r="M111" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" s="20">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="O111" s="20">
-        <v>0</v>
+        <v>685</v>
       </c>
     </row>
     <row r="112" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6543,10 +6543,10 @@
         <v>47</v>
       </c>
       <c r="J112" s="20">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="K112" s="20">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L112" s="20">
         <v>0</v>
@@ -6555,10 +6555,10 @@
         <v>0</v>
       </c>
       <c r="N112" s="20">
-        <v>257</v>
+        <v>102</v>
       </c>
       <c r="O112" s="20">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -6591,22 +6591,22 @@
         <v>101</v>
       </c>
       <c r="J113" s="20">
-        <v>95</v>
+        <v>567</v>
       </c>
       <c r="K113" s="20">
-        <v>0</v>
+        <v>483</v>
       </c>
       <c r="L113" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" s="20">
         <v>0</v>
       </c>
       <c r="N113" s="20">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="O113" s="20">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6639,10 +6639,10 @@
         <v>48</v>
       </c>
       <c r="J114" s="20">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="K114" s="20">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="L114" s="20">
         <v>0</v>
@@ -6651,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="N114" s="20">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="O114" s="20">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6687,22 +6687,22 @@
         <v>49</v>
       </c>
       <c r="J115" s="20">
-        <v>224</v>
+        <v>582</v>
       </c>
       <c r="K115" s="20">
         <v>0</v>
       </c>
       <c r="L115" s="20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M115" s="20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N115" s="20">
         <v>0</v>
       </c>
       <c r="O115" s="20">
-        <v>224</v>
+        <v>575</v>
       </c>
     </row>
     <row r="116" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -6735,7 +6735,7 @@
         <v>81</v>
       </c>
       <c r="J116" s="20">
-        <v>362</v>
+        <v>140</v>
       </c>
       <c r="K116" s="20">
         <v>0</v>
@@ -6750,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="20">
-        <v>362</v>
+        <v>140</v>
       </c>
     </row>
     <row r="117" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6783,22 +6783,22 @@
         <v>102</v>
       </c>
       <c r="J117" s="20">
-        <v>571</v>
+        <v>1134</v>
       </c>
       <c r="K117" s="20">
+        <v>37</v>
+      </c>
+      <c r="L117" s="20">
         <v>3</v>
       </c>
-      <c r="L117" s="20">
-        <v>0</v>
-      </c>
       <c r="M117" s="20">
         <v>0</v>
       </c>
       <c r="N117" s="20">
-        <v>568</v>
+        <v>1054</v>
       </c>
       <c r="O117" s="20">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6831,22 +6831,22 @@
         <v>82</v>
       </c>
       <c r="J118" s="20">
-        <v>325</v>
+        <v>676</v>
       </c>
       <c r="K118" s="20">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L118" s="20">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M118" s="20">
         <v>0</v>
       </c>
       <c r="N118" s="20">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="O118" s="20">
-        <v>325</v>
+        <v>414</v>
       </c>
     </row>
     <row r="119" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -6879,22 +6879,22 @@
         <v>103</v>
       </c>
       <c r="J119" s="20">
-        <v>421</v>
+        <v>923</v>
       </c>
       <c r="K119" s="20">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="L119" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="20">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="N119" s="20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O119" s="20">
-        <v>421</v>
+        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6927,10 +6927,10 @@
         <v>50</v>
       </c>
       <c r="J120" s="20">
-        <v>281</v>
+        <v>976</v>
       </c>
       <c r="K120" s="20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L120" s="20">
         <v>0</v>
@@ -6939,10 +6939,10 @@
         <v>0</v>
       </c>
       <c r="N120" s="20">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="O120" s="20">
-        <v>281</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -6975,7 +6975,7 @@
         <v>120</v>
       </c>
       <c r="J121" s="20">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="K121" s="20">
         <v>0</v>
@@ -6987,10 +6987,10 @@
         <v>0</v>
       </c>
       <c r="N121" s="20">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O121" s="20">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="122" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -7023,13 +7023,13 @@
         <v>51</v>
       </c>
       <c r="J122" s="20">
-        <v>166</v>
+        <v>1026</v>
       </c>
       <c r="K122" s="20">
         <v>0</v>
       </c>
       <c r="L122" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="20">
         <v>0</v>
@@ -7038,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="O122" s="20">
-        <v>166</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="123" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -7071,7 +7071,7 @@
         <v>104</v>
       </c>
       <c r="J123" s="20">
-        <v>496</v>
+        <v>402</v>
       </c>
       <c r="K123" s="20">
         <v>0</v>
@@ -7083,10 +7083,10 @@
         <v>0</v>
       </c>
       <c r="N123" s="20">
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="O123" s="20">
-        <v>0</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="1:15" ht="31" x14ac:dyDescent="0.35">
@@ -7119,7 +7119,7 @@
         <v>121</v>
       </c>
       <c r="J124" s="20">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="K124" s="20">
         <v>0</v>
@@ -7131,10 +7131,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="20">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O124" s="20">
-        <v>128</v>
+        <v>153</v>
       </c>
     </row>
     <row r="125" spans="1:15" ht="46.5" x14ac:dyDescent="0.35">
@@ -7167,7 +7167,7 @@
         <v>83</v>
       </c>
       <c r="J125" s="20">
-        <v>192</v>
+        <v>626</v>
       </c>
       <c r="K125" s="20">
         <v>0</v>
@@ -7179,14 +7179,14 @@
         <v>0</v>
       </c>
       <c r="N125" s="20">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O125" s="20">
-        <v>153</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E125" xr:uid="{E4331598-DD78-4204-8625-2E9E48CF8A6D}"/>
+  <autoFilter ref="B1:B125" xr:uid="{E4331598-DD78-4204-8625-2E9E48CF8A6D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O126">
     <sortCondition ref="C1:C126"/>
   </sortState>
